--- a/log.xlsx
+++ b/log.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="600" windowWidth="19815" windowHeight="6855" tabRatio="727"/>
+    <workbookView xWindow="390" yWindow="600" windowWidth="19815" windowHeight="6855" tabRatio="727" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Master" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="232">
   <si>
     <t>Function</t>
   </si>
@@ -41,160 +41,166 @@
     <t>YEs</t>
   </si>
   <si>
+    <t>Pass 1, Fail 0</t>
+  </si>
+  <si>
     <t>Department</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Pass 1, Fail 1</t>
+  </si>
+  <si>
+    <t>Designation</t>
+  </si>
+  <si>
+    <t>Profession</t>
+  </si>
+  <si>
+    <t>Payment Mode</t>
+  </si>
+  <si>
+    <t>Pass 0, Fail 2</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>classification</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t>Employees</t>
+  </si>
+  <si>
+    <t>CreateAccount</t>
+  </si>
+  <si>
+    <t>Test Case Id</t>
+  </si>
+  <si>
+    <t>Test status</t>
+  </si>
+  <si>
+    <t>Actual status</t>
+  </si>
+  <si>
+    <t>Expected status</t>
+  </si>
+  <si>
+    <t>Url</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>PassWord</t>
+  </si>
+  <si>
+    <t>TC001</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Login successful</t>
+  </si>
+  <si>
+    <t>valid Credentials</t>
+  </si>
+  <si>
+    <t>https://php8.logimaxindia.com/titan_v7/admin/index.php/admin/dashboard</t>
+  </si>
+  <si>
+    <t>Test@1234</t>
+  </si>
+  <si>
+    <t>TC002</t>
+  </si>
+  <si>
+    <t>lmxsupport</t>
+  </si>
+  <si>
+    <t>V6@support</t>
+  </si>
+  <si>
+    <t>TC003</t>
+  </si>
+  <si>
+    <t>Invalid Credentials</t>
+  </si>
+  <si>
+    <t>TC004</t>
+  </si>
+  <si>
+    <t>TC005</t>
+  </si>
+  <si>
+    <t>TC006</t>
+  </si>
+  <si>
+    <t>ddghhhjj</t>
+  </si>
+  <si>
+    <t>TC007</t>
+  </si>
+  <si>
+    <t>Test Status</t>
+  </si>
+  <si>
+    <t>Actual Status</t>
+  </si>
+  <si>
+    <t>Edit(Y/N)</t>
+  </si>
+  <si>
+    <t>EditData</t>
+  </si>
+  <si>
+    <t>Delete(Y/N)</t>
+  </si>
+  <si>
+    <t>pass</t>
+  </si>
+  <si>
+    <t>Department Add successful,search data successfull,Edit department successful,Delete department successful</t>
+  </si>
+  <si>
+    <t>sales</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>Pass 1, Fail 1</t>
-  </si>
-  <si>
-    <t>Designation</t>
-  </si>
-  <si>
-    <t>Profession</t>
-  </si>
-  <si>
-    <t>Payment Mode</t>
-  </si>
-  <si>
-    <t>Pass 0, Fail 2</t>
-  </si>
-  <si>
-    <t>Bank</t>
-  </si>
-  <si>
-    <t>classification</t>
-  </si>
-  <si>
-    <t>customer</t>
-  </si>
-  <si>
-    <t>Employees</t>
-  </si>
-  <si>
-    <t>CreateAccount</t>
-  </si>
-  <si>
-    <t>Test Case Id</t>
-  </si>
-  <si>
-    <t>Test status</t>
-  </si>
-  <si>
-    <t>Actual status</t>
-  </si>
-  <si>
-    <t>Expected status</t>
-  </si>
-  <si>
-    <t>Url</t>
-  </si>
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
-    <t>PassWord</t>
-  </si>
-  <si>
-    <t>TC001</t>
-  </si>
-  <si>
-    <t>valid Credentials</t>
-  </si>
-  <si>
-    <t>https://php8.logimaxindia.com/titan_v7/admin/index.php/admin/dashboard</t>
-  </si>
-  <si>
-    <t>tester</t>
-  </si>
-  <si>
-    <t>Test@1234</t>
-  </si>
-  <si>
-    <t>TC002</t>
-  </si>
-  <si>
-    <t>lmxsupport</t>
-  </si>
-  <si>
-    <t>V6@support</t>
-  </si>
-  <si>
-    <t>TC003</t>
-  </si>
-  <si>
-    <t>Invalid Credentials</t>
-  </si>
-  <si>
-    <t>TC004</t>
-  </si>
-  <si>
-    <t>TC005</t>
-  </si>
-  <si>
-    <t>TC006</t>
-  </si>
-  <si>
-    <t>ddghhhjj</t>
-  </si>
-  <si>
-    <t>TC007</t>
-  </si>
-  <si>
-    <t>Test Status</t>
-  </si>
-  <si>
-    <t>Actual Status</t>
-  </si>
-  <si>
-    <t>Edit(Y/N)</t>
-  </si>
-  <si>
-    <t>EditData</t>
-  </si>
-  <si>
-    <t>Delete(Y/N)</t>
-  </si>
-  <si>
-    <t>pass</t>
-  </si>
-  <si>
-    <t>Department Add successful,search data successfull,Edit department successful,Delete department successful</t>
-  </si>
-  <si>
-    <t>sales</t>
-  </si>
-  <si>
     <t>BranchName</t>
   </si>
   <si>
+    <t>sdfdsf</t>
+  </si>
+  <si>
+    <t>^*&amp;^&amp;&amp;^</t>
+  </si>
+  <si>
+    <t>manager</t>
+  </si>
+  <si>
+    <t>Designation Add successful,search data successfull,Edit designation successful,Delete designation  successful</t>
+  </si>
+  <si>
+    <t>Hiring</t>
+  </si>
+  <si>
+    <t>Junior Hr</t>
+  </si>
+  <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>sdfdsf</t>
-  </si>
-  <si>
-    <t>^*&amp;^&amp;&amp;^</t>
-  </si>
-  <si>
-    <t>manager</t>
-  </si>
-  <si>
-    <t>Designation Add successful,search data successfull,Edit designation successful,Delete designation  successful</t>
-  </si>
-  <si>
-    <t>Hiring</t>
-  </si>
-  <si>
-    <t>Junior Hr</t>
-  </si>
-  <si>
     <t>Designation Add Unsuccessful,search data Unsuccessfull,Edit designation Unsuccessful,Edit department Unsuccessful</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>profession Add successful,search data successfull,Edit profession successful,Delete profession  successful</t>
@@ -989,6 +995,9 @@
   </si>
   <si>
     <t>Text</t>
+  </si>
+  <si>
+    <t>testers</t>
   </si>
 </sst>
 </file>
@@ -1392,95 +1401,98 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
         <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1511,147 +1523,147 @@
   <sheetData>
     <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="N1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="O1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="P1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="R1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="S1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="T1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="U1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="V1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="W1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="X1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Y1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AA1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AB1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AC1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AD1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="G2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="I2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O2">
         <v>641607</v>
       </c>
       <c r="P2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="R2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="S2">
         <v>9878676003</v>
@@ -1660,37 +1672,37 @@
         <v>3535341235</v>
       </c>
       <c r="U2" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="V2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="W2" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="X2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Y2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Z2" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="AA2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AB2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AC2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AD2">
         <v>9875643067</v>
       </c>
       <c r="AE2" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1725,69 +1737,69 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="I2">
         <v>1000</v>
       </c>
       <c r="J2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -1812,42 +1824,48 @@
   <sheetData>
     <row r="1" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" t="s">
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>231</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1855,87 +1873,87 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5">
         <v>3535456</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>3535457</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" t="s">
         <v>33</v>
-      </c>
-      <c r="F8" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1962,48 +1980,48 @@
   <sheetData>
     <row r="1" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2017,7 +2035,7 @@
     </row>
     <row r="4" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="2"/>
@@ -2025,31 +2043,31 @@
         <v>6567</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" t="s">
         <v>49</v>
-      </c>
-      <c r="G4" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2070,48 +2088,48 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2125,25 +2143,25 @@
     </row>
     <row r="4" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3">
         <v>6567</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" t="s">
         <v>49</v>
-      </c>
-      <c r="G4" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2161,48 +2179,48 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2216,25 +2234,25 @@
     </row>
     <row r="4" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D4" s="3">
         <v>6567</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G4" t="s">
         <v>49</v>
-      </c>
-      <c r="G4" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2253,60 +2271,60 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I2" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
@@ -2315,42 +2333,42 @@
     </row>
     <row r="4" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D5" s="3">
         <v>6567</v>
@@ -2359,16 +2377,16 @@
         <v>5535</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="G5" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" t="s">
         <v>49</v>
-      </c>
-      <c r="H5" t="s">
-        <v>74</v>
-      </c>
-      <c r="I5" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2395,96 +2413,96 @@
   <sheetData>
     <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F2">
         <v>780057879</v>
       </c>
       <c r="G2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I2" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="J2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="K2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="L2">
         <v>67452487651</v>
       </c>
       <c r="M2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O2" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -2494,78 +2512,78 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D4">
         <v>4553</v>
       </c>
       <c r="E4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F4">
         <v>641146454</v>
       </c>
       <c r="G4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L4" s="1">
         <v>79879864534</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E5" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I5" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>6576</v>
@@ -2574,16 +2592,16 @@
         <v>77757576</v>
       </c>
       <c r="L5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s">
+        <v>104</v>
+      </c>
+      <c r="N5" t="s">
         <v>102</v>
       </c>
-      <c r="N5" t="s">
-        <v>100</v>
-      </c>
       <c r="O5" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -2610,60 +2628,60 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="G2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I2" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -2671,60 +2689,60 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D4">
         <v>4545</v>
       </c>
       <c r="E4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="G4" t="s">
+        <v>112</v>
+      </c>
+      <c r="H4" t="s">
         <v>110</v>
       </c>
-      <c r="H4" t="s">
-        <v>108</v>
-      </c>
       <c r="I4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F5" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>4234</v>
       </c>
       <c r="H5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I5" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2762,156 +2780,156 @@
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="P1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="Q1" s="7" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="R1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="S1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="T1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="U1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="V1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="W1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="X1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Y1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Z1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AA1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AB1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AC1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AD1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AE1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AF1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AG1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AH1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AI1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AJ1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AK1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AM1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="AN1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AO1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AP1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AQ1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AR1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J2">
         <v>7012180008</v>
@@ -2923,87 +2941,87 @@
         <v>123456</v>
       </c>
       <c r="N2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="Q2" s="8" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="R2" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="S2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="T2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="U2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="V2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="W2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="X2">
         <v>641607</v>
       </c>
       <c r="Y2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Z2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AA2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="AB2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AC2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AD2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AE2" s="10"/>
       <c r="AG2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AH2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AI2">
         <v>9597169176</v>
       </c>
       <c r="AJ2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AK2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AL2" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="AM2">
         <v>9871643545</v>
       </c>
       <c r="AN2" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AO2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AQ2" s="10"/>
       <c r="AR2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.25">
@@ -3018,22 +3036,22 @@
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F4" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J4">
         <v>8939544980</v>
@@ -3045,70 +3063,70 @@
         <v>123456</v>
       </c>
       <c r="N4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P4" s="6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="R4" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="S4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="T4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="U4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="V4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="W4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="X4">
         <v>641607</v>
       </c>
       <c r="Y4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Z4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AA4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AB4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AC4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AF4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AG4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AH4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AI4">
         <v>9597169176</v>
       </c>
       <c r="AJ4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="AK4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.25">
@@ -3120,19 +3138,19 @@
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G6" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J6">
         <v>8939555981</v>
@@ -3144,29 +3162,29 @@
         <v>123456</v>
       </c>
       <c r="N6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P6" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q6" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="R6" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
